--- a/Boeing/boeing_jobs.xlsx
+++ b/Boeing/boeing_jobs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,34 +436,34 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Job ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Role Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Posted Date</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Job Description (Raw)</t>
@@ -476,443 +476,850 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Job Description</t>
+          <t>Hiring details</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Multimedia Illustrations Specialist</t>
+          <t>Typical Tasks</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Basic Qualifications (Required Skills/Experience)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Preferred Qualifications (Desired Skills/Experience)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Equal Opportunity Employer</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Position Responsibilities</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Basic Qualifications (Required Skills/Experience)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Preferred Qualifications (Desired Skills/Experience)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Drug Free Workplace</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Pay &amp; Benefits</t>
+          <t>Physical Demands and Potential Hazards</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Aug. 04, 2025</t>
+          <t>Basic Qualifications</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Relocation</t>
+          <t>Preferred Qualifications</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Security Clearance</t>
+          <t>Typical Education &amp; Experience</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Visa Sponsorship</t>
+          <t>Union Representation Statement</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Shift Work Statement</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Equal Opportunity Employer</t>
+          <t>Total Rewards &amp; Pay Transparency</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>F15 Software</t>
+          <t>The Role</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Our teams are currently hiring for a broad range of experience levels including: Associate, Experienced, and Senior Software Engineers.</t>
+          <t>Responsibilities</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>This position is expected to be 100% onsite. The selected candidate will be required to work onsite at one of the listed location options.</t>
+          <t>Work Authorisation</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Security Clearance and Export Control Requirements</t>
+          <t>Required Qualifications</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>This position requires the ability to obtain a Secret</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Basic Qualifications (Required Skills/ Experience)</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>CodeVue Coding Challenge</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Total Rewards &amp; Pay Transparency</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Aug. 12, 2025</t>
+          <t>Join us if you want to</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Associate Multimedia Illustrations Specialist</t>
+          <t>Experienced Deployment Specialist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Oklahoma City, Oklahoma</t>
+          <t>https://jobs.boeing.com/job/crawley/experienced-deployment-specialist/185/83765182304</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JR2025465606</t>
+          <t>Crawley, England</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>JR2025457694</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Onsite</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Security Clearance</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jul. 28, 2025</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://jobs.boeing.com/job/oklahoma-city/associate-multimedia-illustrations-specialist/185/84344250656</t>
+          <t>Jul. 14, 2025</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Job Description
 At Boeing, we innovate and collaborate to make the world a better place. We’re committed to fostering an environment for every teammate that’s welcoming, respectful and inclusive, with great opportunity for professional growth. Find your future with us.
-Boeing’s Global Services team is seeking a highly motivated, creative and digitally savvy Multimedia Illustrations Specialist to support the Oklahoma City, OK Maintenance Engineering team. This Illustrator will work closely with maintenance and flight manual authors to create, design, and modify detailed illustrations, graphics, and other electronic media in support of technical data products.
-Position Responsibilities:
-Supports creating, designing, and modifying detailed illustrations, graphics, and interactive electronic media using illustration software tools (e.g., IsoDraw, CATIA, AutoTrol)
-Conducts research and analysis of source data or designs to inform illustration and graphics creation
-Adheres to illustration and graphics development standards, processes, and procedures
-Partners with maintenance and flight manual authoring community to ensure product compliance with applicable standards and specifications.
-Applies knowledge of technical illustration principles and techniques for creating graphic representations (e.g., mechanics perspective, isometric drawings, orthographic drawings, wiring diagrams) from technical engineering data
-Coordinates/communicates across the business with internal stakeholders on milestone-driven events
+Boeing Global Services is a leader in providing innovative solutions and services to commercial aviation customers worldwide. Our commitment to excellence in flight training ensures that our airline customers receive the highest quality training content and support.
+We invite enthusiastic candidates who are passionate about aviation safety and quality. If you are ready to contribute to our mission of excellence in flight training, we encourage you to apply to join our team.
+As an Experienced Deployment Specialist, you and your team will publish and distribute flight training course content to Boeing aircraft customers and our flight training campuses. Your expertise will ensure efficient and effective delivery while maintaining content integrity.
+Hiring details:
+This requisition is for a locally hired position in Crawley. Benefits and pay are determined at the local level and are not part of Boeing U.S. based payroll.
+This position is expected to be onsite. The selected candidate will be required to work onsite at one of the listed location options.
+Minimal travel may be required on occasion.
+The role includes being out of home on call during some mornings and weekends for brief overtime assignments, such as responding to outside of working hours support requests at training campuses around the globe. Teammates work on site in Crawley and in the United States.
+Position Responsibilities
+Deploy training courses to customers and internal training campuses
+Manage and maintain our training deployment databases
+Enroll trainees in various training programs
+Protect the integrity of training content throughout its lifecycle
+Typical Tasks:
+Receive direction to publish new and revised flight training media to various distribution channels
+Respond to requests for learning management system access
+Enroll pilots in training courses
+Validate training deployment guidance and metadata
+Assess risks to training operations quality and recommend mitigations
+Support innovative teams in bringing deployment solutions to market
 Basic Qualifications (Required Skills/Experience):
-2+ years of related work experience or an equivalent combination of technical education and experience
-Experience using illustration and graphics development standards (commercial/military specifications)
-Experience in a role that required effective communication across the business
+At least three years of relevant experience in a similar role
 Preferred Qualifications (Desired Skills/Experience):
-Associates degree or higher
-Experience using illustration software tools such as IsoDraw, CATIA, and AutoTrol
-Drug Free Workplace:
-Boeing is a Drug Free Workplace where post offer applicants and employees are subject to testing for marijuana, cocaine, opioids, amphetamines, PCP, and alcohol when criteria is met as outlined in our policies. 
-Pay &amp; Benefits:
-At Boeing, we strive to deliver a Total Rewards package that will attract, engage and retain the top talent.  Elements of the Total Rewards package include competitive base pay and variable compensation opportunities.  
-The Boeing Company also provides eligible employees with an opportunity to enroll in a variety of benefit programs, generally including health insurance, flexible spending accounts, health savings accounts, retirement savings plans, life and disability insurance programs, and a number of programs that provide for both paid and unpaid time away from work.  
-The specific programs and options available to any given employee may vary depending on eligibility factors such as geographic location, date of hire, and the applicability of collective bargaining agreements.
-Pay is based upon candidate experience and qualifications, as well as market and business considerations.  
-Summary Pay Range: $59,500- $80,500
-Applications for this position will be accepted until Aug. 04, 2025
-Export Control Requirements: This position must meet export control compliance requirements. To meet export control compliance requirements, a “U.S. Person” as defined by 22 C.F.R. §120.15 is required. “U.S. Person” includes U.S. Citizen, lawful permanent resident, refugee, or asylee.
-Export Control Details: US based job, US Person required
+Experience in flight training operations
+Knowledge of content management and database recordkeeping
+Commitment to quality and safety and strong attention to detail
+Proficient in computer applications and course content management
+Ability to work independently and on a geographically diverse team
+Integrity to uphold high standards of quality and compliance
+Temperament to provide exceptional customer service to internal and external customers
+The Boeing benefits package goes above and beyond, focusing on your physical, emotional, financial and social well-being. Here’s a snapshot of what we offer: 
+Competitive salary and annual incentive plans 
+Continuous learning - you’ll develop the approach and skills to navigate whatever comes next 
+Success as defined by you - we’ll provide the tools and flexibility, so you can make a meaningful impact, your way 
+Inclusive culture - you’ll be embraced for who you are and empowered to use your voice to help others find theirs 
+Excellent Adoption and Parental leave options 
+23 days plus UK public holidays and a Winter Break between Christmas and New Year 
+Pension Plan with up to 10% employer contribution 
+Company paid BUPA Medical Plan 
+Short Term Sickness: 100% pay for the first 26 weeks 
+Long Term Sickness: 66.67% of annual salary from 27th week 
+6x annual salary life insurance 
+Learning Together Programme to support your on-going personal and career development 
+Access to Boeing’s Well Being Programs, tool and incentives 
+Applications for this position will be accepted until Aug. 31, 2025
+Export Control Requirements: If the successful candidate is not a “U.S. Person“ (as defined by 22 C.F.R. § 120.15 “U.S. Person” includes U.S. citizens, lawful permanent residents, refugees, or asylees) and the position requires access to export-controlled data, an appropriate export authorization by the U.S. Government may be required prior to such access. Employment, and the continuity of employment of non-U.S. persons, is contingent upon the company’s ability to secure and maintain the necessary export control authorization.
+Export Control Details: US based job, US Person not required
 Relocation
 Relocation assistance is not a negotiable benefit for this position.
-Security Clearance
-This position requires the ability to obtain a U.S. Security Clearance for which the U.S. Government requires U.S. Citizenship. An interim and/or final U.S. Secret Clearance Post-Start is required.
 Visa Sponsorship
 Employer will not sponsor applicants for employment visa status.
 Shift
-This position is for 1st shift
+Not a Shift Worker (United Kingdom)
 Equal Opportunity Employer:
-Boeing is an Equal Opportunity Employer. Employment decisions are made without regard to race, color, religion, national origin, gender, sexual orientation, gender identity, age, physical or mental disability, genetic factors, military/veteran status or other characteristics protected by law.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+We are an equal opportunity employer. We do not accept unlawful discrimination in our recruitment or employment practices on any grounds including but not limited to; race, color, ethnicity, religion, national origin, gender, sexual orientation, gender identity, age, physical or mental disability, genetic factors, military and veteran status, or other characteristics covered by applicable law.
+We have teams in more than 65 countries, and each person plays a role in helping us become one of the world’s most innovative, diverse and inclusive companies. We are a Disability Confident Committed employer and welcome applications from candidates with disabilities. Applicants are encouraged to share with our recruitment team any accommodations required during the recruitment process. Accommodations may include but are not limited to: conducting interviews in accessible locations that accommodate mobility needs, encouraging candidates to bring and use any existing assistive technology such as screen readers and offering flexible interview formats such as virtual or phone interviews.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Job Description
+At Boeing, we innovate and collaborate to make the world a better place. We’re committed to fostering an environment for every teammate that’s welcoming, respectful and inclusive, with great opportunity for professional growth. Find your future with us.
+Boeing Global Services is a leader in providing innovative solutions and services to commercial aviation customers worldwide. Our commitment to excellence in flight training ensures that our airline customers receive the highest quality training content and support.
+We invite enthusiastic candidates who are passionate about aviation safety and quality. If you are ready to contribute to our mission of excellence in flight training, we encourage you to apply to join our team.
+As an Experienced Deployment Specialist, you and your team will publish and distribute flight training course content to Boeing aircraft customers and our flight training campuses. Your expertise will ensure efficient and effective delivery while maintaining content integrity.</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>At Boeing, we innovate and collaborate to make the world a better place. We’re committed to fostering an environment for every teammate that’s welcoming, respectful and inclusive, with great opportunity for professional growth. Find your future with us.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Boeing is a Drug Free Workplace where post offer applicants and employees are subject to testing for marijuana, cocaine, opioids, amphetamines, PCP, and alcohol when criteria is met as outlined in our policies.</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>At Boeing, we strive to deliver a Total Rewards package that will attract, engage and retain the top talent.  Elements of the Total Rewards package include competitive base pay and variable compensation opportunities.
-The Boeing Company also provides eligible employees with an opportunity to enroll in a variety of benefit programs, generally including health insurance, flexible spending accounts, health savings accounts, retirement savings plans, life and disability insurance programs, and a number of programs that provide for both paid and unpaid time away from work.
-The specific programs and options available to any given employee may vary depending on eligibility factors such as geographic location, date of hire, and the applicability of collective bargaining agreements.
-Pay is based upon candidate experience and qualifications, as well as market and business considerations.
-Summary Pay Range: $59,500- $80,500</t>
-        </is>
-      </c>
+          <t>This requisition is for a locally hired position in Crawley. Benefits and pay are determined at the local level and are not part of Boeing U.S. based payroll.
+This position is expected to be onsite. The selected candidate will be required to work onsite at one of the listed location options.
+Minimal travel may be required on occasion.
+The role includes being out of home on call during some mornings and weekends for brief overtime assignments, such as responding to outside of working hours support requests at training campuses around the globe. Teammates work on site in Crawley and in the United States.
+Position Responsibilities
+Deploy training courses to customers and internal training campuses
+Manage and maintain our training deployment databases
+Enroll trainees in various training programs
+Protect the integrity of training content throughout its lifecycle</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Receive direction to publish new and revised flight training media to various distribution channels
+Respond to requests for learning management system access
+Enroll pilots in training courses
+Validate training deployment guidance and metadata
+Assess risks to training operations quality and recommend mitigations
+Support innovative teams in bringing deployment solutions to market</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>At least three years of relevant experience in a similar role</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Experience in flight training operations
+Knowledge of content management and database recordkeeping
+Commitment to quality and safety and strong attention to detail
+Proficient in computer applications and course content management
+Ability to work independently and on a geographically diverse team
+Integrity to uphold high standards of quality and compliance
+Temperament to provide exceptional customer service to internal and external customers
+The Boeing benefits package goes above and beyond, focusing on your physical, emotional, financial and social well-being. Here’s a snapshot of what we offer:
+Competitive salary and annual incentive plans
+Continuous learning - you’ll develop the approach and skills to navigate whatever comes next
+Success as defined by you - we’ll provide the tools and flexibility, so you can make a meaningful impact, your way
+Inclusive culture - you’ll be embraced for who you are and empowered to use your voice to help others find theirs
+Excellent Adoption and Parental leave options
+23 days plus UK public holidays and a Winter Break between Christmas and New Year
+Pension Plan with up to 10% employer contribution
+Company paid BUPA Medical Plan
+Short Term Sickness: 100% pay for the first 26 weeks
+Long Term Sickness: 66.67% of annual salary from 27th week
+6x annual salary life insurance
+Learning Together Programme to support your on-going personal and career development
+Access to Boeing’s Well Being Programs, tool and incentives
+Applications for this position will be accepted until Aug. 31, 2025
+Export Control Requirements: If the successful candidate is not a “U.S. Person“ (as defined by 22 C.F.R. § 120.15 “U.S. Person” includes U.S. citizens, lawful permanent residents, refugees, or asylees) and the position requires access to export-controlled data, an appropriate export authorization by the U.S. Government may be required prior to such access. Employment, and the continuity of employment of non-U.S. persons, is contingent upon the company’s ability to secure and maintain the necessary export control authorization.
+Export Control Details: US based job, US Person not required
+Relocation
+Relocation assistance is not a negotiable benefit for this position.
+Visa Sponsorship
+Employer will not sponsor applicants for employment visa status.
+Shift
+Not a Shift Worker (United Kingdom)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>We are an equal opportunity employer. We do not accept unlawful discrimination in our recruitment or employment practices on any grounds including but not limited to; race, color, ethnicity, religion, national origin, gender, sexual orientation, gender identity, age, physical or mental disability, genetic factors, military and veteran status, or other characteristics covered by applicable law.
+We have teams in more than 65 countries, and each person plays a role in helping us become one of the world’s most innovative, diverse and inclusive companies. We are a Disability Confident Committed employer and welcome applications from candidates with disabilities. Applicants are encouraged to share with our recruitment team any accommodations required during the recruitment process. Accommodations may include but are not limited to: conducting interviews in accessible locations that accommodate mobility needs, encouraging candidates to bring and use any existing assistive technology such as screen readers and offering flexible interview formats such as virtual or phone interviews.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Relocation assistance is not a negotiable benefit for this position.</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>This position requires the ability to obtain a U.S. Security Clearance for which the U.S. Government requires U.S. Citizenship. An interim and/or final U.S. Secret Clearance Post-Start is required.</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Employer will not sponsor applicants for employment visa status.</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>This position is for 1st shift</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Boeing is an Equal Opportunity Employer. Employment decisions are made without regard to race, color, religion, national origin, gender, sexual orientation, gender identity, age, physical or mental disability, genetic factors, military/veteran status or other characteristics protected by law.</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F15 Software Engineers (Associate, Experienced or Senior Level)</t>
+          <t>Silk Screener Decorative Panels B - 79805</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Berkeley, Missouri</t>
+          <t>https://jobs.boeing.com/job/everett/silk-screener-decorative-panels-b-79805/185/83661188480</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JR2025465562</t>
+          <t>Everett, Washington</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>JR2025462962</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Onsite</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Engineering - Software</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jul. 28, 2025</t>
+          <t>All Hourly Unions</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://jobs.boeing.com/job/berkeley/f15-software-engineers-associate-experienced-or-senior-level/185/84344250592</t>
+          <t>Jul. 11, 2025</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Job Description
 At Boeing, we innovate and collaborate to make the world a better place. We’re committed to fostering an environment for every teammate that’s welcoming, respectful and inclusive, with great opportunity for professional growth. Find your future with us.
-The Boeing Company is currently seeking F15 Software Engineers (Associate, Experienced, or Senior Level) to join the Special Equipment Group (SEG) located in Berkeley, MO. This position will focus on supporting the Boeing Defense, Space &amp; Security (BDS) business organization.
-A proprietary program is expanding its business and is looking for additional software engineers to support product development. The products are part of analysis systems used by combat personnel and include algorithmic analysis as well as data management.  The customer is expanding product capabilities to support the fielding of new systems and to incorporate new technologies.  This proprietary program attracts new business as a result of user community recognition. 
-The product target OS is Windows running on PCs. All products are developed using .NET C# within a strong object-oriented architecture. The Integrated Development Environment for source code and GUI development is Microsoft Visual Studio.  Automated unit and integration testing are developed in C# using a custom C# framework for automated integration testing using UI Automation. Qualification testing is manual and is performed on the target PC hardware. Developer work stations consist of a development tech PC and a PC for external access.
-Our teams are currently hiring for a broad range of experience levels including: Associate, Experienced, and Senior Software Engineers.
+Boeing Commercial Airplanes is excited to offer opportunities for a Silk Screener Decorative Panels B to join our Joint and Installation team in Everett Washington.
+Join our innovative team as a Silk Screener for Decorative Panels. In this dynamic position, you will set up and execute multicolor silk screen printing operations, ensuring precise alignment and registration to create stunning instrument panels. Your expertise in mixing and matching paints will guarantee that each print meets our high standards for color consistency and clarity. Collaborating closely with various departments, you will coordinate the distribution of decals and maintain an organized inventory, all while adhering to safety regulations for hazardous materials. If you are passionate about combining creativity with technical skill in a fast-paced environment, we invite you to be a part of our mission to deliver exceptional decorative solutions.
+You will play a critical role in upholding our commitment to safety and quality standards, ensuring that all operations meet regulatory compliance and operational excellence. If you are detail-oriented, possess strong technical skills, and thrive in a collaborative environment, we invite you to apply and be a part of our mission to deliver excellence in aviation.
 Position Responsibilities:
-Define software requirements
-Design, develop, integrate, and test software in C#/Windows Presentation Foundation (WPF)
-Participate in an Agile scrum team
-Implement new features and enhancements
-Investigate and resolve software problem reports / bugs
-Works under general direction
+Set up and perform multicolor decorative silk screen printing operations according to established procedures.
+Align and adjust the silk screen to achieve proper contact and registration, applying paint using the squeegee method.
+Layout, locate, and apply lettering on various instrument panels using silk screening and related processes.
+Liaise with the Decal Area and other departments to coordinate changes, distribution of decals, and maintain perpetual inventory.
+Work from blueprints, specifications, and verbal instructions to complete assignments accurately.
+Clean silk screens and maintain tools and equipment to ensure quality printing.
+Mix and match paint to established color samples, ensuring consistency and accuracy.
+Obtain work orders and necessary materials, including inks and substrates, while adhering to safety data sheet guidelines.
+Perform hand setup for contact printing, including loading silk screens and applying ink to substrates.
+Operate the silk screen machine, managing the printing process for multiple colors and ensuring quality control.
+Check ink color using a color spectrometer and make adjustments as needed to match specifications.
+Perform rework and touch-ups on decorative interior parts using appropriate tools and techniques.
+Handle and dispose of hazardous materials in compliance with safety regulations.
+Maintain records of work performed and refile work packets in the ink room filing cabinet.
+Communicate with team leaders and supervisors regarding job progress, issues, and assistance needed.
+Physical Demands and Potential Hazards:
+Perform physical tasks that include lifting weights ranging from 10-15 lbs. to 15-35 lbs.
+Engage in various movements such as reaching, handling, turning, twisting, lifting, lowering, climbing, balancing, bending, kneeling, crouching, and squatting.
+Work in environments that may involve contact with metals, solvents, and coolants.
+Operate in proximity to moving parts and tools, sharp cutters, and potential slipping hazards.
+Adapt to varying noise levels and atmospheric conditions.
+Utilize personal safety gear to protect face/eyes, hands/arms, and feet while performing job duties.
 This position is expected to be 100% onsite. The selected candidate will be required to work onsite at one of the listed location options.
-Security Clearance and Export Control Requirements:
-This position requires the ability to obtain a SecretUS Security Clearance for which the US Government requires US Citizenship.  Ability to obtain Secret US Security clearance (Post-Start).
-Basic Qualifications (Required Skills/ Experience):
-2 plus years’ experience as a software engineer
-1 plus years’ experience with C# and .NET
-Great communications and writing skills (Critical thinking skills; flexible team environment)
-Preferred Qualifications (Desired Skills/Experience):
-Bachelor of Science degree from an accredited course of study, in Computer Engineering, Software Engineering, Computer Science, or other technical degree
-Design experience within a layered software architecture using Object Oriented (OO) Design and Analysis concepts along with OO Design Pattern application is required
-Experience with Agile development methodologies
-A solid history of using the aforementioned tools, languages, and techniques to develop applications for Windows based PC applications
-Development experience using C# and WPF is strongly desired
-Familiarity with SQL and SQL Server is desired
-Familiarity with agile methodologies such as scrum or SAFe
-Knowledgeable in tools such as Jenkins, Git, Jira, BitBucket and Visual Studio
-Drug Free Workplace:
-Boeing is a Drug Free Workplace where post offer applicants and employees are subject to testing for marijuana, cocaine, opioids, amphetamines, PCP, and alcohol when criteria is met as outlined in our policies.
-CodeVue Coding Challenge:
-To be considered for this position you will be required to complete a technical assessment as part of the selection process. Failure to complete the assessment will remove you from consideration.
+This position must meet Export Control compliance requirements, therefore a “US Person” as defined by 22 C.F.R. § 120.15 is required. “US Person” includes US Citizen, lawful permanent resident, refugee, or asylee
+Current Boeing employees working in Puget Sound must submit an Employee Request Transfer (ERT) to be considered in the eligible candidate pool. Resumes of current Puget Sound Boeing employees submitted via Careers at Boeing will not be considered.
+Basic Qualifications:
+1+ years of experience silk screen printing.
+Experience mixing and color matching water based inks.
+Experience handling and disposing of hazardous materials per government regulations.
+Ability to recognize colors.
+Ability to walk constantly throughout the workday; stand 6-8 hours per day; climb or work from stairs/steps up to 8 hours per day; climb ladders; bend and twist frequently up to six hours per day; squat and kneel. 
+This position requires you to wear eye, hearing, foot, hand, respirator and other personal protective equipment/safety gear at all times.  
+Preferred Qualifications:
+Perform ink formulation (e.g. measure ink by weight, machine mix ink, apply ink to test specimen, dry in oven).
+Experience working with overhead crane.
+Enrolled in a Boeing partnered manufacturing related high school or community and technology college academic program  
+Typical Education &amp; Experience:
+High school graduate or GED preferred.
+Drug Free Workplace
+Boeing is a Drug Free Workplace where post offer applicants and employees are subject to testing for marijuana, cocaine, opioids, amphetamines, PCP, and alcohol when criteria is met as outlined in our policies.
+Union Representation Statement:
+This is an hourly position governed by the International Association of Machinists (IAM-751) Collective Bargaining agreement.
+Shift Work Statement:
+This position is for a variety of shifts
 Total Rewards &amp; Pay Transparency:
 At Boeing, we strive to deliver a Total Rewards package that will attract, engage and retain the top talent.  Elements of the Total Rewards package include competitive base pay and variable compensation opportunities.  
 The Boeing Company also provides eligible employees with an opportunity to enroll in a variety of benefit programs, generally including health insurance, flexible spending accounts, health savings accounts, retirement savings plans, life and disability insurance programs, and a number of programs that provide for both paid and unpaid time away from work.  
 The specific programs and options available to any given employee may vary depending on eligibility factors such as geographic location, date of hire, and the applicability of collective bargaining agreements.
-Please note that the salary information shown below is a general guideline only.  Salaries are based upon candidate experience and qualifications, as well as market and business considerations.  
-Summary pay range for Associate: $85,000.00 - $115,000.00.
-Summary pay range for Experienced: $104,550.00 - $141,450.00.
-Summary pay range for Senior: $127,500.00 - $172,500.00.
-Applications for this position will be accepted until Aug. 12, 2025
-Export Control Requirements: This position must meet export control compliance requirements. To meet export control compliance requirements, a “U.S. Person” as defined by 22 C.F.R. §120.15 is required. “U.S. Person” includes U.S. Citizen, lawful permanent resident, refugee, or asylee.
-Export Control Details: US based job, US Person required
+Pay is based upon candidate experience and qualifications, as well as market and business considerations.  
+Summary pay range: $25.00 – $49.92 per hour
+Applications for this position will be accepted until Jan. 11, 2026
+Language Requirements
+English Preferred
 Relocation
-This position offers relocation based on candidate eligibility.
-Security Clearance
-This position requires the ability to obtain a U.S. Security Clearance for which the U.S. Government requires U.S. Citizenship. An interim and/or final U.S. Secret Clearance Post-Start is required.
+Relocation assistance is not a negotiable benefit for this position.
 Visa Sponsorship
 Employer will not sponsor applicants for employment visa status.
 Shift
-This position is for 1st shift
+This position is for variable shift
 Equal Opportunity Employer:
 Boeing is an Equal Opportunity Employer. Employment decisions are made without regard to race, color, religion, national origin, gender, sexual orientation, gender identity, age, physical or mental disability, genetic factors, military/veteran status or other characteristics protected by law.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>At Boeing, we innovate and collaborate to make the world a better place. We’re committed to fostering an environment for every teammate that’s welcoming, respectful and inclusive, with great opportunity for professional growth. Find your future with us.</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Job Description
+At Boeing, we innovate and collaborate to make the world a better place. We’re committed to fostering an environment for every teammate that’s welcoming, respectful and inclusive, with great opportunity for professional growth. Find your future with us.
+Boeing Commercial Airplanes is excited to offer opportunities for a Silk Screener Decorative Panels B to join our Joint and Installation team in Everett Washington.
+Join our innovative team as a Silk Screener for Decorative Panels. In this dynamic position, you will set up and execute multicolor silk screen printing operations, ensuring precise alignment and registration to create stunning instrument panels. Your expertise in mixing and matching paints will guarantee that each print meets our high standards for color consistency and clarity. Collaborating closely with various departments, you will coordinate the distribution of decals and maintain an organized inventory, all while adhering to safety regulations for hazardous materials. If you are passionate about combining creativity with technical skill in a fast-paced environment, we invite you to be a part of our mission to deliver exceptional decorative solutions.
+You will play a critical role in upholding our commitment to safety and quality standards, ensuring that all operations meet regulatory compliance and operational excellence. If you are detail-oriented, possess strong technical skills, and thrive in a collaborative environment, we invite you to apply and be a part of our mission to deliver excellence in aviation.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Define software requirements
-Design, develop, integrate, and test software in C#/Windows Presentation Foundation (WPF)
-Participate in an Agile scrum team
-Implement new features and enhancements
-Investigate and resolve software problem reports / bugs
-Works under general direction</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Bachelor of Science degree from an accredited course of study, in Computer Engineering, Software Engineering, Computer Science, or other technical degree
-Design experience within a layered software architecture using Object Oriented (OO) Design and Analysis concepts along with OO Design Pattern application is required
-Experience with Agile development methodologies
-A solid history of using the aforementioned tools, languages, and techniques to develop applications for Windows based PC applications
-Development experience using C# and WPF is strongly desired
-Familiarity with SQL and SQL Server is desired
-Familiarity with agile methodologies such as scrum or SAFe
-Knowledgeable in tools such as Jenkins, Git, Jira, BitBucket and Visual Studio</t>
+          <t>Boeing is an Equal Opportunity Employer. Employment decisions are made without regard to race, color, religion, national origin, gender, sexual orientation, gender identity, age, physical or mental disability, genetic factors, military/veteran status or other characteristics protected by law.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Boeing is a Drug Free Workplace where post offer applicants and employees are subject to testing for marijuana, cocaine, opioids, amphetamines, PCP, and alcohol when criteria is met as outlined in our policies.</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+          <t>Set up and perform multicolor decorative silk screen printing operations according to established procedures.
+Align and adjust the silk screen to achieve proper contact and registration, applying paint using the squeegee method.
+Layout, locate, and apply lettering on various instrument panels using silk screening and related processes.
+Liaise with the Decal Area and other departments to coordinate changes, distribution of decals, and maintain perpetual inventory.
+Work from blueprints, specifications, and verbal instructions to complete assignments accurately.
+Clean silk screens and maintain tools and equipment to ensure quality printing.
+Mix and match paint to established color samples, ensuring consistency and accuracy.
+Obtain work orders and necessary materials, including inks and substrates, while adhering to safety data sheet guidelines.
+Perform hand setup for contact printing, including loading silk screens and applying ink to substrates.
+Operate the silk screen machine, managing the printing process for multiple colors and ensuring quality control.
+Check ink color using a color spectrometer and make adjustments as needed to match specifications.
+Perform rework and touch-ups on decorative interior parts using appropriate tools and techniques.
+Handle and dispose of hazardous materials in compliance with safety regulations.
+Maintain records of work performed and refile work packets in the ink room filing cabinet.
+Communicate with team leaders and supervisors regarding job progress, issues, and assistance needed.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Perform physical tasks that include lifting weights ranging from 10-15 lbs. to 15-35 lbs.
+Engage in various movements such as reaching, handling, turning, twisting, lifting, lowering, climbing, balancing, bending, kneeling, crouching, and squatting.
+Work in environments that may involve contact with metals, solvents, and coolants.
+Operate in proximity to moving parts and tools, sharp cutters, and potential slipping hazards.
+Adapt to varying noise levels and atmospheric conditions.
+Utilize personal safety gear to protect face/eyes, hands/arms, and feet while performing job duties.
+This position is expected to be 100% onsite. The selected candidate will be required to work onsite at one of the listed location options.
+This position must meet Export Control compliance requirements, therefore a “US Person” as defined by 22 C.F.R. § 120.15 is required. “US Person” includes US Citizen, lawful permanent resident, refugee, or asylee
+Current Boeing employees working in Puget Sound must submit an Employee Request Transfer (ERT) to be considered in the eligible candidate pool. Resumes of current Puget Sound Boeing employees submitted via Careers at Boeing will not be considered.</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1+ years of experience silk screen printing.
+Experience mixing and color matching water based inks.
+Experience handling and disposing of hazardous materials per government regulations.
+Ability to recognize colors.
+Ability to walk constantly throughout the workday; stand 6-8 hours per day; climb or work from stairs/steps up to 8 hours per day; climb ladders; bend and twist frequently up to six hours per day; squat and kneel.
+This position requires you to wear eye, hearing, foot, hand, respirator and other personal protective equipment/safety gear at all times.</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>This position offers relocation based on candidate eligibility.</t>
+          <t>Perform ink formulation (e.g. measure ink by weight, machine mix ink, apply ink to test specimen, dry in oven).
+Experience working with overhead crane.
+Enrolled in a Boeing partnered manufacturing related high school or community and technology college academic program</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>This position requires the ability to obtain a U.S. Security Clearance for which the U.S. Government requires U.S. Citizenship. An interim and/or final U.S. Secret Clearance Post-Start is required.</t>
+          <t>High school graduate or GED preferred.
+Drug Free Workplace
+Boeing is a Drug Free Workplace where post offer applicants and employees are subject to testing for marijuana, cocaine, opioids, amphetamines, PCP, and alcohol when criteria is met as outlined in our policies.</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Employer will not sponsor applicants for employment visa status.</t>
+          <t>This is an hourly position governed by the International Association of Machinists (IAM-751) Collective Bargaining agreement.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>This position is for 1st shift</t>
+          <t>This position is for a variety of shifts</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Boeing is an Equal Opportunity Employer. Employment decisions are made without regard to race, color, religion, national origin, gender, sexual orientation, gender identity, age, physical or mental disability, genetic factors, military/veteran status or other characteristics protected by law.</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>A proprietary program is expanding its business and is looking for additional software engineers to support product development. The products are part of analysis systems used by combat personnel and include algorithmic analysis as well as data management.  The customer is expanding product capabilities to support the fielding of new systems and to incorporate new technologies.  This proprietary program attracts new business as a result of user community recognition.
-The product target OS is Windows running on PCs. All products are developed using .NET C# within a strong object-oriented architecture. The Integrated Development Environment for source code and GUI development is Microsoft Visual Studio.  Automated unit and integration testing are developed in C# using a custom C# framework for automated integration testing using UI Automation. Qualification testing is manual and is performed on the target PC hardware. Developer work stations consist of a development tech PC and a PC for external access.</t>
-        </is>
-      </c>
+          <t>At Boeing, we strive to deliver a Total Rewards package that will attract, engage and retain the top talent.  Elements of the Total Rewards package include competitive base pay and variable compensation opportunities.
+The Boeing Company also provides eligible employees with an opportunity to enroll in a variety of benefit programs, generally including health insurance, flexible spending accounts, health savings accounts, retirement savings plans, life and disability insurance programs, and a number of programs that provide for both paid and unpaid time away from work.
+The specific programs and options available to any given employee may vary depending on eligibility factors such as geographic location, date of hire, and the applicability of collective bargaining agreements.
+Pay is based upon candidate experience and qualifications, as well as market and business considerations.
+Summary pay range: $25.00 – $49.92 per hour
+Applications for this position will be accepted until Jan. 11, 2026
+Language Requirements
+English Preferred
+Relocation
+Relocation assistance is not a negotiable benefit for this position.
+Visa Sponsorship
+Employer will not sponsor applicants for employment visa status.
+Shift
+This position is for variable shift</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>2 plus years’ experience as a software engineer
-1 plus years’ experience with C# and .NET
-Great communications and writing skills (Critical thinking skills; flexible team environment)</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>To be considered for this position you will be required to complete a technical assessment as part of the selection process. Failure to complete the assessment will remove you from consideration.</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>At Boeing, we strive to deliver a Total Rewards package that will attract, engage and retain the top talent.  Elements of the Total Rewards package include competitive base pay and variable compensationopportunities.
-The Boeing Company also provides eligible employees with an opportunity to enroll in a variety of benefit programs, generally including health insurance, flexible spending accounts, health savings accounts, retirement savings plans, life and disability insurance programs, and a number of programs that provide for both paid and unpaid time away from work.
-The specific programs and options available to any given employee may vary depending on eligibility factors such as geographic location, date of hire, and the applicability of collective bargaining agreements.
-Please note that the salary information shown below is a general guideline only.  Salaries are based upon candidate experience and qualifications, as well as market and businessconsiderations.
-Summary pay range for Associate: $85,000.00 - $115,000.00.
-Summary pay range for Experienced: $104,550.00 - $141,450.00.
-Summary pay range for Senior: $127,500.00 - $172,500.00.</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Senior Programme Manager</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://jobs.boeing.com/job/frimley/senior-programme-manager/185/78568309856</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Frimley, England; Dublin, Leinster</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>JR2025447017</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Program Management</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Jul. 11, 2025</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Job Description
+At Boeing, we innovate and collaborate to make the world a better place. We’re committed to fostering an environment for every teammate that’s welcoming, respectful and inclusive, with great opportunity for professional growth. Find your future with us.
+With more than a century of experience, Boeing’s knowledge in bringing innovative service solutions to commercial, defence and space customers has united to form Boeing Global Services.
+With a focus on innovative services in engineering, digital aviation and analytics as well as supply chain logistics and training support, Boeing will deliver agile, cost-competitive solutions, regardless of the original equipment manufacturer, so customers can reduce costs, drive efficiency and optimize operations.
+The Role:
+We are seeking applicants to join our rapidly expanding, world class team managing changes to aircraft for our global airline partners. We will support you to develop your already substantial skills and encourage you to reach your career goals.
+This is a senior Programme Management role.
+You will manage the post-delivery modification of aircraft interiors, involving the integration of new equipment into the aircraft. We frequently manage multiple stakeholders providing equipment and services to the Customer. Working together with the Engineering, Airworthiness and logistics teams you will manage the execution of the project within the schedule and budgetary constraints agreed.
+Previous experience of aircraft modification projects would be a distinct advantage and would suit applicants with Programme Management or Project Engineering backgrounds in aerospace environments or MRO’s.
+The successful candidate will work within the Boeing Global Services Programme Management team, based in either Frimley, Surrey or Dublin, Ireland.
+Responsibilities:
+Act as focal point for the company to worldwide airline customers
+Complete program ownership of delivery schedule, meeting quality standards, and financial controls from project award to final delivery
+Identify and manage program risks, issues and opportunities to protect or improve the program performance
+Lead internal program teams to execute the program requirements
+Coordinate internal activities to ensure all tasks are progressing in line with the program requirements
+Coordinate and lead major milestone meetings with the customer (ITCM, PDR, CDR, FAI) and compile resulting minutes and action plans
+Portray the customers’ expectations and requirements to the Engineering team to ensure alignment
+Provide weekly status updates, milestone schedules and risk analysis summaries
+Communicate program status, on-going financial viability and identification of key issues to senior management
+Manage customer change requests and support proposals for schedule and cost related impact
+Initiate invoicing of project payments and follow-up on payment as required
+Supports the creation of proposals, as required, in response to customer RFPs
+Work Authorisation:
+This requisition is for a locally hired position in either the UK or Ireland. Candidates must have current legal authorisation to work immediately in the UK or Ireland.
+Boeing will not attempt to obtain Immigration and labour sponsorship for any applicants.
+Benefits and pay are determined at the local level and are not part of Boeing U.S. based payroll. This position does not have relocation approval.
+Required Qualifications:
+Qualification in Program Management or equivalent preferred (PMP or CPM, etc.)
+Previous experience of aircraft modification / integration projects would be advantageous
+Work within and Engineering environment, ideally within the aerospace industry
+Minimum 10 years of applicable experience required
+Proficient in all MS Office applications required, including MS Project
+Ability to travel up to 50% of the time, sometimes at short notice
+Able to work independently without high levels of supervision (self-motivated)
+Ideally have a minimum BS Degree in a STEM field and/or at least 5 years' experience in a related commercial/military aerospace business.
+The Boeing benefits package goes above and beyond, focusing on your physical, emotional, financial and social well-being. Here’s a snapshot of what we offer:
+Competitive salary and annual incentive plans
+Continuous learning - you’ll develop the mindset and skills to navigate whatever comes next
+Success as defined by you - we’ll provide the tools and flexibility, so you can make a meaningful impact, your way
+Diverse and inclusive culture - you’ll be embraced for who you are and empowered to use your voice to help others find theirs
+Learning Together Programme to support your on-going personal and career development
+Access to Boeing’s Well Being Programs, tool and incentives
+Applications for this position will be accepted until Sept. 11, 2025
+Relocation
+Relocation assistance is not a negotiable benefit for this position.
+Visa Sponsorship
+Employer will not sponsor applicants for employment visa status.
+Equal Opportunity Employer:
+We are an equal opportunity employer. We do not accept unlawful discrimination in our recruitment or employment practices on any grounds including but not limited to; race, color, ethnicity, religion, national origin, gender, sexual orientation, gender identity, age, physical or mental disability, genetic factors, military and veteran status, or other characteristics covered by applicable law.
+We have teams in more than 65 countries, and each person plays a role in helping us become one of the world’s most innovative, diverse and inclusive companies. We are a Disability Confident Committed employer and welcome applications from candidates with disabilities. Applicants are encouraged to share with our recruitment team any accommodations required during the recruitment process. Accommodations may include but are not limited to: conducting interviews in accessible locations that accommodate mobility needs, encouraging candidates to bring and use any existing assistive technology such as screen readers and offering flexible interview formats such as virtual or phone interviews.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Job Description
+At Boeing, we innovate and collaborate to make the world a better place. We’re committed to fostering an environment for every teammate that’s welcoming, respectful and inclusive, with great opportunity for professional growth. Find your future with us.
+With more than a century of experience, Boeing’s knowledge in bringing innovative service solutions to commercial, defence and space customers has united to form Boeing Global Services.
+With a focus on innovative services in engineering, digital aviation and analytics as well as supply chain logistics and training support, Boeing will deliver agile, cost-competitive solutions, regardless of the original equipment manufacturer, so customers can reduce costs, drive efficiency and optimize operations.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>We are an equal opportunity employer. We do not accept unlawful discrimination in our recruitment or employment practices on any grounds including but not limited to; race, color, ethnicity, religion, national origin, gender, sexual orientation, gender identity, age, physical or mental disability, genetic factors, military and veteran status, or other characteristics covered by applicable law.
+We have teams in more than 65 countries, and each person plays a role in helping us become one of the world’s most innovative, diverse and inclusive companies. We are a Disability Confident Committed employer and welcome applications from candidates with disabilities. Applicants are encouraged to share with our recruitment team any accommodations required during the recruitment process. Accommodations may include but are not limited to: conducting interviews in accessible locations that accommodate mobility needs, encouraging candidates to bring and use any existing assistive technology such as screen readers and offering flexible interview formats such as virtual or phone interviews.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>We are seeking applicants to join our rapidly expanding, world class team managing changes to aircraft for our global airline partners. We will support you to develop your already substantial skills and encourage you to reach your career goals.
+This is a senior Programme Management role.
+You will manage the post-delivery modification of aircraft interiors, involving the integration of new equipment into the aircraft. We frequently manage multiple stakeholders providing equipment and services to the Customer. Working together with the Engineering, Airworthiness and logistics teams you will manage the execution of the project within the schedule and budgetary constraints agreed.
+Previous experience of aircraft modification projects would be a distinct advantage and would suit applicants with Programme Management or Project Engineering backgrounds in aerospace environments or MRO’s.
+The successful candidate will work within the Boeing Global Services Programme Management team, based in either Frimley, Surrey or Dublin, Ireland.</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Act as focal point for the company to worldwide airline customers
+Complete program ownership of delivery schedule, meeting quality standards, and financial controls from project award to final delivery
+Identify and manage program risks, issues and opportunities to protect or improve the program performance
+Lead internal program teams to execute the program requirements
+Coordinate internal activities to ensure all tasks are progressing in line with the program requirements
+Coordinate and lead major milestone meetings with the customer (ITCM, PDR, CDR, FAI) and compile resulting minutes and action plans
+Portray the customers’ expectations and requirements to the Engineering team to ensure alignment
+Provide weekly status updates, milestone schedules and risk analysis summaries
+Communicate program status, on-going financial viability and identification of key issues to senior management
+Manage customer change requests and support proposals for schedule and cost related impact
+Initiate invoicing of project payments and follow-up on payment as required
+Supports the creation of proposals, as required, in response to customer RFPs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>This requisition is for a locally hired position in either the UK or Ireland. Candidates must have current legal authorisation to work immediately in the UK or Ireland.
+Boeing will not attempt to obtain Immigration and labour sponsorship for any applicants.
+Benefits and pay are determined at the local level and are not part of Boeing U.S. based payroll. This position does not have relocation approval.</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Qualification in Program Management or equivalent preferred (PMP or CPM, etc.)
+Previous experience of aircraft modification / integration projects would be advantageous
+Work within and Engineering environment, ideally within the aerospace industry
+Minimum 10 years of applicable experience required
+Proficient in all MS Office applications required, including MS Project
+Ability to travel up to 50% of the time, sometimes at short notice
+Able to work independently without high levels of supervision (self-motivated)
+Ideally have a minimum BS Degree in a STEM field and/or at least 5 years' experience in a related commercial/military aerospace business.
+The Boeing benefits package goes above and beyond, focusing on your physical, emotional, financial and social well-being. Here’s a snapshot of what we offer:
+Competitive salary and annual incentive plans
+Continuous learning - you’ll develop the mindset and skills to navigate whatever comes next
+Success as defined by you - we’ll provide the tools and flexibility, so you can make a meaningful impact, your way
+Diverse and inclusive culture - you’ll be embraced for who you are and empowered to use your voice to help others find theirs
+Learning Together Programme to support your on-going personal and career development
+Access to Boeing’s Well Being Programs, tool and incentives
+Applications for this position will be accepted until Sept. 11, 2025
+Relocation
+Relocation assistance is not a negotiable benefit for this position.
+Visa Sponsorship
+Employer will not sponsor applicants for employment visa status.</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Associate AvionX MBD Software Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://jobs.boeing.com/job/gdansk/associate-avionx-mbd-software-engineer/185/83648107088</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Gdansk, Pomerania; Warsaw, Mazovia; Rzeszów, Subcarpathia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>JR2025463428</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Engineering - Software</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>lip. 11, 2025</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Job Description
+At Boeing, we innovate and collaborate to make the world a better place. We’re committed to fostering an environment for every teammate that’s welcoming, respectful and inclusive, with great opportunity for professional growth. Find your future with us.
+Boeing Poland Software Engineering develops and produces avionics and electronics systems designed for use on aircraft and other platforms for purposes such as navigation, flight controls, information systems, and other core avionics functions. We have set our sights high – to design, develop, and manufacture the most technically advanced and reliable avionic components in the world. We are innovating and developing new products to address the future of the urban air mobility as well as our next generation of commercial, tactical, and trainer aircraft markets.
+As an Associate AvionX MBD Software Engineer the job holder will join the Software Engineering team consisting of highly skilled, high performing engineering team members supporting multiple product lines across Boeing organization.
+Hiring details:
+This requisition is for a locally hired position in Gdansk, Rzeszów or Warsaw. Benefits and pay are determined at the local level and are not part of Boeing U.S. based payroll.
+This position is expected to be onsite. The selected candidate will be required to work onsite at one of the listed location options.
+Position Responsibilities:
+Model development: Support the development of systems and models using tools like MATLAB and Simulink. This involves creating block diagrams, specifying system behavior, and implementing algorithms
+Simulation and analysis: Use simulation techniques to analyze the behavior of the system model under different conditions and inputs. This includes running simulations and analyzing results
+System integration: Support integration of the system models with other components or subsystems
+Verification and validation: development and maintenance of unit testing, integration testing, and system-level testing to ensure the model behaves as expected
+Working with requirements: This involves requirements development and proper interpretation of software requirements while creating and developing models
+Collaborate with cross-functional teams: contributing to development process of certain system components
+Creating technical documentation, user manuals, and design specifications
+Continuously improve skills and knowledge through training, self-study, and participation in professional development activities
+Basic Qualifications (Required Skills/Experience):
+2+ year of professional experience
+English proficiency
+Preferred Qualifications (Desired Skills/Experience):
+Programming skills in MATLAB, Simulink, and C/C++ is essential. Knowledge of scripting languages like Python can also be beneficial
+Elementary knowledge of building models, simulating systems, analyzing simulation results, and code generation in MBD approach
+System-level thinking: This includes understanding system requirements, architecture, and integration
+Willingness to develop safety critical software and models according to DO-178C and DO-331
+Familiarity with software development cycle such as version control, testing methodologies, agile development and CI/CD
+Ability to identify issues, and propose effective solutions
+Continuous learning: Willingness to learn and adapt to new technologies, tools, and methodologies
+Collaborating in international and multi-national projects
+Join us if you want to:
+Market competitive salary and performance-based incentive program
+Have flexible working hours 
+Enjoy additional paid days off for Christmas break (December 24th-January 1st) 
+Broaden your experience in international software projects, technical workshops, and hackathons
+Develop professional skills with our virtual learning tools and platforms 
+Benefit from Learning Together Program and MyBenefit program 
+Benefit from Employee Recognition Program 
+Get Medical Plan (Medicover/LuxMed) and life insurance (Warta S.A.) for you and your Family 
+Participate in Employee Pension Scheme (PPE) 
+Enjoy and create with us a friendly and inclusive atmosphere in the workplace 
+Cooperate and exchange knowledge with international team where we support and respect each other 
+Applications for this position will be accepted until Aug. 17, 2025
+Export Control Requirements: This is not an Export Control position.
+Relocation
+Relocation assistance is not a negotiable benefit for this position.
+Visa Sponsorship
+Employer will not sponsor applicants for employment visa status.
+Shift
+Not a Shift Worker (Poland)
+Equal Opportunity Employer:
+We are an equal opportunity employer. We do not accept unlawful discrimination in our recruitment or employment practices on any grounds including but not limited to; race, color, ethnicity, religion, national origin, gender, sexual orientation, gender identity, age, physical or mental disability, genetic factors, military and veteran status, or other characteristics covered by applicable law.
+We have teams in more than 65 countries, and each person plays a role in helping us become one of the world’s most innovative, diverse and inclusive companies. We are proud members of the Valuable 500  and welcome applications from candidates with disabilities. Applicants are encouraged to share with our recruitment team any accommodations required during the recruitment process. Accommodations may include but are not limited to: conducting interviews in accessible locations that accommodate mobility needs, encouraging candidates to bring and use any existing assistive technology such as screen readers and offering flexible interview formats such as virtual or phone interviews.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Job Description
+At Boeing, we innovate and collaborate to make the world a better place. We’re committed to fostering an environment for every teammate that’s welcoming, respectful and inclusive, with great opportunity for professional growth. Find your future with us.
+Boeing Poland Software Engineering develops and produces avionics and electronics systems designed for use on aircraft and other platforms for purposes such as navigation, flight controls, information systems, and other core avionics functions. We have set our sights high – to design, develop, and manufacture the most technically advanced and reliable avionic components in the world. We are innovating and developing new products to address the future of the urban air mobility as well as our next generation of commercial, tactical, and trainer aircraft markets.
+As an Associate AvionX MBD Software Engineer the job holder will join the Software Engineering team consisting of highly skilled, high performing engineering team members supporting multiple product lines across Boeing organization.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>This requisition is for a locally hired position in Gdansk, Rzeszów or Warsaw. Benefits and pay are determined at the local level and are not part of Boeing U.S. based payroll.
+This position is expected to be onsite. The selected candidate will be required to work onsite at one of the listed location options.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2+ year of professional experience
+English proficiency</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Programming skills in MATLAB, Simulink, and C/C++ is essential. Knowledge of scripting languages like Python can also be beneficial
+Elementary knowledge of building models, simulating systems, analyzing simulation results, and code generation in MBD approach
+System-level thinking: This includes understanding system requirements, architecture, and integration
+Willingness to develop safety critical software and models according to DO-178C and DO-331
+Familiarity with software development cycle such as version control, testing methodologies, agile development and CI/CD
+Ability to identify issues, and propose effective solutions
+Continuous learning: Willingness to learn and adapt to new technologies, tools, and methodologies
+Collaborating in international and multi-national projects</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>We are an equal opportunity employer. We do not accept unlawful discrimination in our recruitment or employment practices on any grounds including but not limited to; race, color, ethnicity, religion, national origin, gender, sexual orientation, gender identity, age, physical or mental disability, genetic factors, military and veteran status, or other characteristics covered by applicable law.
+We have teams in more than 65 countries, and each person plays a role in helping us become one of the world’s most innovative, diverse and inclusive companies. We are proud members of the Valuable 500  and welcome applications from candidates with disabilities. Applicants are encouraged to share with our recruitment team any accommodations required during the recruitment process. Accommodations may include but are not limited to: conducting interviews in accessible locations that accommodate mobility needs, encouraging candidates to bring and use any existing assistive technology such as screen readers and offering flexible interview formats such as virtual or phone interviews.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Model development: Support the development of systems and models using tools like MATLAB and Simulink. This involves creating block diagrams, specifying system behavior, and implementing algorithms
+Simulation and analysis: Use simulation techniques to analyze the behavior of the system model under different conditions and inputs. This includes running simulations and analyzing results
+System integration: Support integration of the system models with other components or subsystems
+Verification and validation: development and maintenance of unit testing, integration testing, and system-level testing to ensure the model behaves as expected
+Working with requirements: This involves requirements development and proper interpretation of software requirements while creating and developing models
+Collaborate with cross-functional teams: contributing to development process of certain system components
+Creating technical documentation, user manuals, and design specifications
+Continuously improve skills and knowledge through training, self-study, and participation in professional development activities</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Market competitive salary and performance-based incentive program
+Have flexible working hours
+Enjoy additional paid days off for Christmas break (December 24th-January 1st)
+Broaden your experience in international software projects, technical workshops, and hackathons
+Develop professional skills with our virtual learning tools and platforms
+Benefit from Learning Together Program and MyBenefit program
+Benefit from Employee Recognition Program
+Get Medical Plan (Medicover/LuxMed) and life insurance (Warta S.A.) for you and your Family
+Participate in Employee Pension Scheme (PPE)
+Enjoy and create with us a friendly and inclusive atmosphere in the workplace
+Cooperate and exchange knowledge with international team where we support and respect each other
+Applications for this position will be accepted until Aug. 17, 2025
+Export Control Requirements: This is not an Export Control position.
+Relocation
+Relocation assistance is not a negotiable benefit for this position.
+Visa Sponsorship
+Employer will not sponsor applicants for employment visa status.
+Shift
+Not a Shift Worker (Poland)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
